--- a/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,03</t>
+          <t>2,76; 12,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 22,26</t>
+          <t>10,85; 22,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,39</t>
+          <t>4,47; 13,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 16,19</t>
+          <t>4,32; 16,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,07</t>
+          <t>3,94; 13,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 17,64</t>
+          <t>7,55; 17,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 13,06</t>
+          <t>3,5; 12,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 13,93</t>
+          <t>2,84; 13,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,06</t>
+          <t>4,23; 10,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 17,77</t>
+          <t>10,24; 17,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 11,2</t>
+          <t>5,0; 10,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 12,01</t>
+          <t>4,32; 12,09</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,4</t>
+          <t>3,44; 9,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,45</t>
+          <t>5,94; 13,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,27</t>
+          <t>7,56; 15,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,17</t>
+          <t>3,83; 10,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,62</t>
+          <t>5,78; 12,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 14,12</t>
+          <t>6,69; 13,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 12,25</t>
+          <t>6,1; 12,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 18,09</t>
+          <t>9,43; 18,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,53</t>
+          <t>5,33; 9,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 12,41</t>
+          <t>6,9; 12,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 12,55</t>
+          <t>7,38; 12,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,09</t>
+          <t>7,43; 13,2</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 11,04</t>
+          <t>2,82; 10,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,19</t>
+          <t>5,15; 15,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 13,79</t>
+          <t>5,57; 13,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,81</t>
+          <t>4,1; 10,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 17,63</t>
+          <t>6,98; 17,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 15,89</t>
+          <t>5,71; 14,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,12</t>
+          <t>1,59; 7,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,75</t>
+          <t>2,48; 7,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,01</t>
+          <t>6,39; 13,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,45</t>
+          <t>6,6; 13,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,31</t>
+          <t>4,04; 9,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,84</t>
+          <t>3,98; 8,18</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 11,66</t>
+          <t>4,7; 12,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 12,34</t>
+          <t>4,24; 12,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,62</t>
+          <t>2,66; 9,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,3</t>
+          <t>2,43; 7,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,0</t>
+          <t>2,46; 7,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,59</t>
+          <t>2,8; 9,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,35</t>
+          <t>3,03; 10,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 12,08</t>
+          <t>5,33; 11,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,91</t>
+          <t>4,34; 9,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,2</t>
+          <t>4,02; 9,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,65</t>
+          <t>3,68; 8,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,85</t>
+          <t>4,74; 8,76</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,53</t>
+          <t>5,06; 8,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,53</t>
+          <t>8,05; 12,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,48</t>
+          <t>6,66; 10,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,65</t>
+          <t>4,54; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,94</t>
+          <t>6,36; 10,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,56</t>
+          <t>7,33; 11,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,45</t>
+          <t>5,07; 8,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,31</t>
+          <t>6,52; 10,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,62</t>
+          <t>6,0; 8,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 11,27</t>
+          <t>8,21; 11,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,9</t>
+          <t>6,39; 9,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 8,59</t>
+          <t>6,02; 8,46</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4895</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16395</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8360</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13292</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6849</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4117</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11765</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29687</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15209</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>9071</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2170; 9433</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11301; 23776</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4594; 13357</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2484; 9207</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3482; 12047</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8462; 19474</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3417; 11877</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1744; 8355</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7068; 18216</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>22129; 38691</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10011; 21935</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5134; 14383</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14423</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16878</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10056</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16209</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18891</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18194</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>23910</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>27364</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>33314</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>35072</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>33966</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6433; 17464</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9468; 20734</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11768; 24215</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6089; 16490</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10907; 24040</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12929; 26930</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12838; 26512</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>17125; 33284</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>20054; 36604</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>24335; 43554</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>27011; 45425</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>25288; 44960</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9026</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12871</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11964</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12120</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9936</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4949</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>9407</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>17346</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18961</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17820</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>21371</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2429; 9209</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5046; 14783</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8036; 19669</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7058; 18722</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7204; 18387</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5810; 15206</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2099; 9915</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5280; 16848</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>12096; 24599</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13182; 26405</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>11177; 25299</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>15302; 31499</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>11684</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8645</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12463</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7268</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7753</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>24652</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>18636</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15913</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14367</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>37116</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7074; 18143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4894; 14558</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3250; 11615</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6598; 19906</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3637; 11652</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3681; 12493</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3944; 13790</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>16230; 35197</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12957; 26981</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>9935; 23323</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9279; 22071</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>27309; 50482</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>32961</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48489</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44723</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>62086</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>75112</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>82468</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>101524</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>25409; 43683</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38389; 61454</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>34963; 56558</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29988; 51536</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>33619; 53681</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>39493; 62706</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>28904; 49272</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>49592; 77792</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>61797; 89101</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>83350; 114106</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>70008; 99045</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>85519; 120247</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,01</t>
+          <t>2,63; 12,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 22,84</t>
+          <t>10,26; 22,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 13,01</t>
+          <t>4,44; 13,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 16,01</t>
+          <t>4,58; 15,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 13,62</t>
+          <t>3,89; 13,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 17,38</t>
+          <t>7,51; 17,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 12,17</t>
+          <t>3,52; 12,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,6</t>
+          <t>2,72; 14,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,91</t>
+          <t>4,2; 11,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 17,9</t>
+          <t>9,99; 17,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,95</t>
+          <t>4,97; 11,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,09</t>
+          <t>4,45; 12,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,33</t>
+          <t>3,59; 9,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 13,01</t>
+          <t>5,65; 13,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 15,57</t>
+          <t>7,21; 15,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,38</t>
+          <t>3,72; 10,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 12,74</t>
+          <t>5,7; 12,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,69; 13,94</t>
+          <t>6,66; 13,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,59</t>
+          <t>5,8; 12,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 18,32</t>
+          <t>9,25; 18,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,74</t>
+          <t>5,17; 9,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,35</t>
+          <t>7,05; 12,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,41</t>
+          <t>7,28; 12,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 13,2</t>
+          <t>7,45; 13,26</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,71</t>
+          <t>2,87; 11,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 15,09</t>
+          <t>5,03; 15,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,63</t>
+          <t>5,56; 13,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,86</t>
+          <t>4,0; 11,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 17,81</t>
+          <t>6,77; 17,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 14,94</t>
+          <t>5,9; 15,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,5</t>
+          <t>1,57; 7,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,93</t>
+          <t>2,32; 7,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 13,0</t>
+          <t>6,18; 12,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 13,22</t>
+          <t>6,45; 13,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,15</t>
+          <t>4,18; 9,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,18</t>
+          <t>3,7; 7,89</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,06</t>
+          <t>4,88; 12,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 12,6</t>
+          <t>4,08; 12,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,51</t>
+          <t>2,77; 10,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,33</t>
+          <t>2,62; 7,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,87</t>
+          <t>2,57; 8,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,49</t>
+          <t>2,82; 9,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,61</t>
+          <t>3,26; 10,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,55</t>
+          <t>5,31; 11,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,04</t>
+          <t>4,17; 8,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,43</t>
+          <t>4,04; 9,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,75</t>
+          <t>3,45; 8,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,76</t>
+          <t>4,73; 9,12</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,7</t>
+          <t>4,96; 8,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,88</t>
+          <t>8,18; 12,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,78</t>
+          <t>6,62; 10,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,81</t>
+          <t>4,47; 7,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,16</t>
+          <t>6,19; 10,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,64</t>
+          <t>7,1; 11,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,64</t>
+          <t>5,02; 8,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,23</t>
+          <t>6,46; 10,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,64</t>
+          <t>5,97; 8,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,23</t>
+          <t>8,18; 11,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,04</t>
+          <t>6,2; 8,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,46</t>
+          <t>6,09; 8,67</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2170; 9433</t>
+          <t>2070; 9547</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11301; 23776</t>
+          <t>10687; 22966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4594; 13357</t>
+          <t>4559; 13390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2484; 9207</t>
+          <t>2635; 8865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3482; 12047</t>
+          <t>3441; 11580</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8462; 19474</t>
+          <t>8417; 19478</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3417; 11877</t>
+          <t>3439; 11728</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1744; 8355</t>
+          <t>1671; 8948</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7068; 18216</t>
+          <t>7023; 18511</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22129; 38691</t>
+          <t>21598; 38624</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10011; 21935</t>
+          <t>9947; 22104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5134; 14383</t>
+          <t>5290; 14714</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6433; 17464</t>
+          <t>6713; 17545</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9468; 20734</t>
+          <t>8997; 21038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11768; 24215</t>
+          <t>11222; 23615</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6089; 16490</t>
+          <t>5905; 16145</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10907; 24040</t>
+          <t>10756; 23023</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12929; 26930</t>
+          <t>12871; 26553</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12838; 26512</t>
+          <t>12208; 25724</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17125; 33284</t>
+          <t>16813; 34399</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20054; 36604</t>
+          <t>19454; 35988</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24335; 43554</t>
+          <t>24839; 43487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27011; 45425</t>
+          <t>26661; 45502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25288; 44960</t>
+          <t>25354; 45148</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2429; 9209</t>
+          <t>2471; 9520</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5046; 14783</t>
+          <t>4925; 15065</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8036; 19669</t>
+          <t>8027; 19918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7058; 18722</t>
+          <t>6898; 19329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7204; 18387</t>
+          <t>6990; 18296</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5810; 15206</t>
+          <t>6012; 15447</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2099; 9915</t>
+          <t>2074; 9396</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5280; 16848</t>
+          <t>4931; 16730</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12096; 24599</t>
+          <t>11688; 24329</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13182; 26405</t>
+          <t>12895; 26708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11177; 25299</t>
+          <t>11545; 25258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15302; 31499</t>
+          <t>14221; 30359</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7074; 18143</t>
+          <t>7344; 18424</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4894; 14558</t>
+          <t>4710; 14642</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3250; 11615</t>
+          <t>3384; 12611</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6598; 19906</t>
+          <t>7105; 20052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3637; 11652</t>
+          <t>3801; 11950</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3681; 12493</t>
+          <t>3714; 12982</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3944; 13790</t>
+          <t>4235; 13814</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16230; 35197</t>
+          <t>16185; 35094</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12957; 26981</t>
+          <t>12448; 25541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9935; 23323</t>
+          <t>9992; 22876</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9279; 22071</t>
+          <t>8697; 21089</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27309; 50482</t>
+          <t>27278; 52571</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25409; 43683</t>
+          <t>24919; 42812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38389; 61454</t>
+          <t>39011; 60340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34963; 56558</t>
+          <t>34721; 55716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29988; 51536</t>
+          <t>29505; 50292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33619; 53681</t>
+          <t>32699; 53374</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39493; 62706</t>
+          <t>38238; 61357</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28904; 49272</t>
+          <t>28628; 48785</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49592; 77792</t>
+          <t>49117; 77960</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61797; 89101</t>
+          <t>61541; 88920</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83350; 114106</t>
+          <t>83051; 113810</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70008; 99045</t>
+          <t>67923; 96114</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85519; 120247</t>
+          <t>86545; 123106</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,66%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,23%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15,75%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 12,15</t>
+          <t>3,84; 13,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,26; 22,06</t>
+          <t>7,5; 17,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 13,04</t>
+          <t>3,6; 13,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 15,41</t>
+          <t>2,67; 13,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 13,09</t>
+          <t>2,81; 12,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 17,38</t>
+          <t>10,29; 22,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,01</t>
+          <t>4,43; 13,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 14,56</t>
+          <t>4,69; 17,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,08</t>
+          <t>4,36; 11,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 17,87</t>
+          <t>10,13; 17,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,03</t>
+          <t>5,22; 11,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 12,37</t>
+          <t>4,59; 12,59</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,85%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,37</t>
+          <t>5,85; 12,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 13,2</t>
+          <t>6,52; 14,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,18</t>
+          <t>5,7; 12,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,16</t>
+          <t>8,13; 16,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 12,2</t>
+          <t>3,65; 9,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,74</t>
+          <t>6,12; 13,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 12,22</t>
+          <t>7,33; 15,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 18,93</t>
+          <t>4,0; 10,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,57</t>
+          <t>5,32; 9,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 12,33</t>
+          <t>6,99; 12,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 12,43</t>
+          <t>7,32; 12,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 13,26</t>
+          <t>7,01; 12,5</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,08%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,21%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8,92%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,07</t>
+          <t>7,25; 17,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,38</t>
+          <t>5,66; 15,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 13,8</t>
+          <t>1,67; 7,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 11,21</t>
+          <t>2,37; 7,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 17,72</t>
+          <t>2,43; 11,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 15,17</t>
+          <t>5,03; 15,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,11</t>
+          <t>5,36; 13,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 7,87</t>
+          <t>4,19; 10,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,85</t>
+          <t>6,24; 13,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 13,37</t>
+          <t>6,2; 13,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,14</t>
+          <t>4,2; 9,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,89</t>
+          <t>3,74; 7,85</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,77%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,48%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,25</t>
+          <t>2,51; 8,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,67</t>
+          <t>2,84; 9,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,33</t>
+          <t>2,94; 10,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,38</t>
+          <t>5,73; 12,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,07</t>
+          <t>4,78; 11,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,86</t>
+          <t>4,1; 12,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,63</t>
+          <t>2,73; 9,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,52</t>
+          <t>3,12; 7,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,56</t>
+          <t>4,36; 8,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,25</t>
+          <t>4,21; 9,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,36</t>
+          <t>3,58; 8,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,12</t>
+          <t>5,0; 9,12</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,52</t>
+          <t>6,3; 9,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,65</t>
+          <t>7,17; 11,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,62</t>
+          <t>5,07; 8,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,62</t>
+          <t>6,14; 9,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,1</t>
+          <t>4,96; 8,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,39</t>
+          <t>7,93; 12,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,55</t>
+          <t>6,55; 10,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,25</t>
+          <t>4,92; 8,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,63</t>
+          <t>5,97; 8,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,2</t>
+          <t>8,28; 11,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,78</t>
+          <t>6,37; 8,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,67</t>
+          <t>6,02; 8,56</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13292</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6849</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4895</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>16395</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>8360</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4954</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6870</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13292</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6849</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8280</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2070; 9547</t>
+          <t>3396; 11561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10687; 22966</t>
+          <t>8399; 19764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4559; 13390</t>
+          <t>3510; 12752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2635; 8865</t>
+          <t>1351; 7067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3441; 11580</t>
+          <t>2205; 9453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8417; 19478</t>
+          <t>10716; 23174</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3439; 11728</t>
+          <t>4550; 13754</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1671; 8948</t>
+          <t>2441; 9259</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7023; 18511</t>
+          <t>7277; 18470</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21598; 38624</t>
+          <t>21902; 38411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9947; 22104</t>
+          <t>10459; 22443</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5290; 14714</t>
+          <t>4708; 12921</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16209</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18891</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18194</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18837</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14423</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16878</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10056</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16209</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18891</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18194</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33966</t>
+          <t>28487</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6713; 17545</t>
+          <t>11035; 23812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8997; 21038</t>
+          <t>12604; 27280</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11222; 23615</t>
+          <t>12006; 25805</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5905; 16145</t>
+          <t>12750; 25891</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10756; 23023</t>
+          <t>6842; 17603</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12871; 26553</t>
+          <t>9754; 21429</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12208; 25724</t>
+          <t>11406; 23747</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16813; 34399</t>
+          <t>5806; 15157</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19454; 35988</t>
+          <t>20012; 35812</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24839; 43487</t>
+          <t>24661; 43765</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26661; 45502</t>
+          <t>26804; 45934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25354; 45148</t>
+          <t>21168; 37751</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9936</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4949</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8877</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9026</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12871</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11964</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12120</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9936</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21041</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2471; 9520</t>
+          <t>7489; 18210</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4925; 15065</t>
+          <t>5766; 16179</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8027; 19918</t>
+          <t>2208; 9407</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6898; 19329</t>
+          <t>4738; 15634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6990; 18296</t>
+          <t>2087; 9501</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6012; 15447</t>
+          <t>4932; 14880</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2074; 9396</t>
+          <t>7732; 19898</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4931; 16730</t>
+          <t>7293; 18956</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11688; 24329</t>
+          <t>11819; 24622</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12895; 26708</t>
+          <t>12392; 26880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11545; 25258</t>
+          <t>11604; 25731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14221; 30359</t>
+          <t>13979; 29376</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6952</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7268</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23833</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>11684</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8645</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6614</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12463</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6952</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7268</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7753</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37116</t>
+          <t>36742</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7344; 18424</t>
+          <t>3719; 11843</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4710; 14642</t>
+          <t>3743; 12628</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3384; 12611</t>
+          <t>3818; 13461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7105; 20052</t>
+          <t>16725; 35575</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3801; 11950</t>
+          <t>7191; 17545</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3714; 12982</t>
+          <t>4732; 14255</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4235; 13814</t>
+          <t>3335; 11742</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16185; 35094</t>
+          <t>7867; 19803</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12448; 25541</t>
+          <t>13001; 26602</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9992; 22876</t>
+          <t>10402; 22752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8697; 21089</t>
+          <t>9029; 21798</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27278; 52571</t>
+          <t>27205; 49570</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>54913</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>94550</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24919; 42812</t>
+          <t>33274; 52542</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39011; 60340</t>
+          <t>38616; 62296</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34721; 55716</t>
+          <t>28893; 48170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29505; 50292</t>
+          <t>42903; 69325</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32699; 53374</t>
+          <t>24916; 42840</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38238; 61357</t>
+          <t>37802; 59783</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28628; 48785</t>
+          <t>34354; 55005</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49117; 77960</t>
+          <t>30673; 51187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61541; 88920</t>
+          <t>61548; 88815</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83051; 113810</t>
+          <t>84091; 114490</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67923; 96114</t>
+          <t>69808; 97438</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86545; 123106</t>
+          <t>79571; 113243</t>
         </is>
       </c>
     </row>
